--- a/Assets/Game/luban/config/general/rename_cost.xlsx
+++ b/Assets/Game/luban/config/general/rename_cost.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -41,16 +41,19 @@
     <t>#name</t>
   </si>
   <si>
+    <t>rename_count</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>interval</t>
-  </si>
-  <si>
-    <t>priority_item</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
   </si>
   <si>
     <t>list#sep=|,priority_item</t>
@@ -1317,27 +1320,27 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:5">
@@ -1345,10 +1348,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1356,13 +1359,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1370,13 +1373,13 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Game/luban/config/general/rename_cost.xlsx
+++ b/Assets/Game/luban/config/general/rename_cost.xlsx
@@ -86,7 +86,7 @@
     <t>2;2</t>
   </si>
   <si>
-    <t>20001;1;0|10001;10;1</t>
+    <t>110001;1;0|100001;10;1</t>
   </si>
   <si>
     <t>其他情况</t>
@@ -95,7 +95,7 @@
     <t>3;0</t>
   </si>
   <si>
-    <t>20001;1;0|10001;20;1</t>
+    <t>110001;1;0|100001;20;1</t>
   </si>
 </sst>
 </file>
